--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A53FB71-4E84-45E6-B846-EB09D06C1010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230043D4-59DB-4FBE-9BC0-AB9A28EC9CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-9210" windowWidth="21810" windowHeight="15930" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>Part Number</t>
   </si>
@@ -39,9 +39,6 @@
     <t>SCH/TP4056.SchLib</t>
   </si>
   <si>
-    <t>PCB Path</t>
-  </si>
-  <si>
     <t>PCB/TP4056.PcbLib</t>
   </si>
   <si>
@@ -49,13 +46,46 @@
   </si>
   <si>
     <t>Library Ref</t>
+  </si>
+  <si>
+    <t>SOP8-PP_TPW</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>PartID</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>https://dlnmh9ip6v2uc.cloudfront.net/datasheets/Prototyping/TP4056.pdf</t>
+  </si>
+  <si>
+    <t>TempMax</t>
+  </si>
+  <si>
+    <t>TempMin</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>1A single cell</t>
+  </si>
+  <si>
+    <t>charger for single cell lithium-ion batteries</t>
+  </si>
+  <si>
+    <t>Library Path</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,16 +93,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -80,14 +131,73 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Check Cell" xfId="1" builtinId="23"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -366,49 +476,97 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="84.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" customWidth="1"/>
+    <col min="10" max="10" width="20.85546875" customWidth="1"/>
+    <col min="11" max="11" width="96.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2">
+        <v>-40</v>
+      </c>
+      <c r="F2" s="2">
+        <v>85</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="I2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
+      <c r="K2" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{62464DCE-AF39-4603-AA20-32EE7D0AF916}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K0000FF internal</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230043D4-59DB-4FBE-9BC0-AB9A28EC9CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF6B926-266A-45C5-8B65-E53E055E3D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
   <si>
     <t>Part Number</t>
   </si>
@@ -79,13 +79,118 @@
   </si>
   <si>
     <t>Library Path</t>
+  </si>
+  <si>
+    <t>SK12D07VG4</t>
+  </si>
+  <si>
+    <t>0.3A @ 30 VDC</t>
+  </si>
+  <si>
+    <t>Slide Switches - Side Knob</t>
+  </si>
+  <si>
+    <t>https://www.snapeda.com/parts/SK12D07VG4/C&amp;K/datasheet/</t>
+  </si>
+  <si>
+    <t>SCH/SK12D07VG4.SchLib</t>
+  </si>
+  <si>
+    <t>PCB/SK12D07VG4.PcbLib</t>
+  </si>
+  <si>
+    <t>1N5819HW-7-F</t>
+  </si>
+  <si>
+    <t>Vf = 450 mV</t>
+  </si>
+  <si>
+    <t>Schottky Diodes &amp; Rectifiers SOD-123</t>
+  </si>
+  <si>
+    <t>SOD3715X145N</t>
+  </si>
+  <si>
+    <t>PCB/SOD3715X145N.PcbLib</t>
+  </si>
+  <si>
+    <t>SCH/1N5819HW-7-F.SchLib</t>
+  </si>
+  <si>
+    <t>https://4donline.ihs.com/images/VipMasterIC/IC/DIOD/DIOD-S-A0011437026/DIOD-S-A0011683586-1.pdf?hkey=CECEF36DEECDED6468708AAF2E19C0C6</t>
+  </si>
+  <si>
+    <t>PJ-002A</t>
+  </si>
+  <si>
+    <t>2.5A @ 24 VDC</t>
+  </si>
+  <si>
+    <t>DC Power Connectors Power Jacks 2x5.5mm</t>
+  </si>
+  <si>
+    <t>CUI_PJ-002A</t>
+  </si>
+  <si>
+    <t>SCH/PJ-002A.SchLib</t>
+  </si>
+  <si>
+    <t>PCB/CUI_PJ-002A.PcbLib</t>
+  </si>
+  <si>
+    <t>https://www.sameskydevices.com/product/resource/pj-002a.pdf</t>
+  </si>
+  <si>
+    <t>Switch Tactile Button 12x12mm</t>
+  </si>
+  <si>
+    <t>FP-MJTP1212A-MFG</t>
+  </si>
+  <si>
+    <t>SCH/button_12mm.SchLib</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/omron-electronics-inc-emc-div/B3F-4055/31799?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=19971370784&amp;gbraid=0AAAAADrbLlgb8g5iB56Pq7GBfmlW8M2um&amp;gclid=CjwKCAiA2svIBhB-EiwARWDPjsxJrtH3aqZi4wzUZvXY0ugmwA-CuPqPru_7AumdmvXcQLZq2TM71hoCQyEQAvD_BwE</t>
+  </si>
+  <si>
+    <t>PCB/button_12mm.PcbLib</t>
+  </si>
+  <si>
+    <t>CMP-47024-000003-1</t>
+  </si>
+  <si>
+    <t>BSS84W-7-F</t>
+  </si>
+  <si>
+    <t>0 V 130mA</t>
+  </si>
+  <si>
+    <t>MOSFET P-Channel 50V 130MA SOT323</t>
+  </si>
+  <si>
+    <t>SOT65P222X110-3N</t>
+  </si>
+  <si>
+    <t>SCH/BSS84W-7-F.SchLib</t>
+  </si>
+  <si>
+    <t>PCB/SOT65P222X110-3N.PcbLib</t>
+  </si>
+  <si>
+    <t>https://www.diodes.com/assets/Datasheets/BSS84W.pdf</t>
+  </si>
+  <si>
+    <t>MJTP1212A</t>
+  </si>
+  <si>
+    <t>0.05A @ 12VDC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +210,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -476,18 +587,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="13.85546875" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" customWidth="1"/>
     <col min="4" max="4" width="84.5703125" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" customWidth="1"/>
-    <col min="10" max="10" width="20.85546875" customWidth="1"/>
-    <col min="11" max="11" width="96.42578125" customWidth="1"/>
+    <col min="7" max="7" width="27.42578125" customWidth="1"/>
+    <col min="8" max="8" width="33.5703125" customWidth="1"/>
+    <col min="9" max="9" width="30.140625" customWidth="1"/>
+    <col min="10" max="10" width="43" customWidth="1"/>
+    <col min="11" max="11" width="136.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -560,9 +673,190 @@
         <v>11</v>
       </c>
     </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2">
+        <v>-20</v>
+      </c>
+      <c r="F3" s="2">
+        <v>70</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2">
+        <v>-65</v>
+      </c>
+      <c r="F4" s="2">
+        <v>125</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="2">
+        <v>-25</v>
+      </c>
+      <c r="F5" s="2">
+        <v>85</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-25</v>
+      </c>
+      <c r="F6" s="2">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-55</v>
+      </c>
+      <c r="F7" s="2">
+        <v>150</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{62464DCE-AF39-4603-AA20-32EE7D0AF916}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{3FCFAC1E-539B-45DA-A95A-A3E2C9FBD5DE}"/>
+    <hyperlink ref="K4" r:id="rId3" xr:uid="{68653B32-FEC9-4DDA-9148-9C376AE5E821}"/>
+    <hyperlink ref="K5" r:id="rId4" xr:uid="{61CA21C5-C988-48A1-A8A2-F9FD15B491E5}"/>
+    <hyperlink ref="K6" r:id="rId5" display="https://www.digikey.de/de/products/detail/omron-electronics-inc-emc-div/B3F-4055/31799?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=19971370784&amp;gbraid=0AAAAADrbLlgb8g5iB56Pq7GBfmlW8M2um&amp;gclid=CjwKCAiA2svIBhB-EiwARWDPjsxJrtH3aqZi4wzUZvXY0ugmwA-CuPqPru_7AumdmvXcQLZq2TM71hoCQyEQAvD_BwE" xr:uid="{E4FF004C-5A6C-4B6D-9D01-B58BD91062E9}"/>
+    <hyperlink ref="K7" r:id="rId6" xr:uid="{78F5BECE-FB68-4FD0-9323-150479BC1E56}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF6B926-266A-45C5-8B65-E53E055E3D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B146A557-C6A1-4B28-A7C6-5A91FFD510DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
   <si>
     <t>Part Number</t>
   </si>
@@ -184,6 +184,27 @@
   </si>
   <si>
     <t>0.05A @ 12VDC</t>
+  </si>
+  <si>
+    <t>ESP32-DEVKIT-V1</t>
+  </si>
+  <si>
+    <t>Dual Core, Wi-Fi, BLE</t>
+  </si>
+  <si>
+    <t>ESP32-DEVKIT-V1 30 Pins</t>
+  </si>
+  <si>
+    <t>MODULE_ESP32_DEVKIT_V1</t>
+  </si>
+  <si>
+    <t>PCB/MODULE_ESP32_DEVKIT_V1.PcbLib</t>
+  </si>
+  <si>
+    <t>SCH/ESP32-DEVKIT-V1.SchLib</t>
+  </si>
+  <si>
+    <t>https://www.snapeda.com/parts/ESP32-DEVKIT-V1/Do+it/view-part/?ref=eda</t>
   </si>
 </sst>
 </file>
@@ -291,7 +312,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -304,6 +325,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -587,10 +611,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="19.85546875" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" customWidth="1"/>
     <col min="4" max="4" width="84.5703125" customWidth="1"/>
@@ -626,10 +650,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>2</v>
@@ -661,10 +685,10 @@
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>4</v>
@@ -696,10 +720,10 @@
         <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>23</v>
@@ -731,10 +755,10 @@
         <v>24</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>28</v>
@@ -766,10 +790,10 @@
         <v>31</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>36</v>
@@ -801,10 +825,10 @@
         <v>43</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>42</v>
@@ -836,16 +860,51 @@
         <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>49</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="2">
+        <v>-40</v>
+      </c>
+      <c r="F8" s="2">
+        <v>85</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -857,6 +916,7 @@
     <hyperlink ref="K5" r:id="rId4" xr:uid="{61CA21C5-C988-48A1-A8A2-F9FD15B491E5}"/>
     <hyperlink ref="K6" r:id="rId5" display="https://www.digikey.de/de/products/detail/omron-electronics-inc-emc-div/B3F-4055/31799?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=19971370784&amp;gbraid=0AAAAADrbLlgb8g5iB56Pq7GBfmlW8M2um&amp;gclid=CjwKCAiA2svIBhB-EiwARWDPjsxJrtH3aqZi4wzUZvXY0ugmwA-CuPqPru_7AumdmvXcQLZq2TM71hoCQyEQAvD_BwE" xr:uid="{E4FF004C-5A6C-4B6D-9D01-B58BD91062E9}"/>
     <hyperlink ref="K7" r:id="rId6" xr:uid="{78F5BECE-FB68-4FD0-9323-150479BC1E56}"/>
+    <hyperlink ref="K8" r:id="rId7" xr:uid="{229173BB-844E-4007-BA9D-092EC23AECD2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B146A557-C6A1-4B28-A7C6-5A91FFD510DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BDD44A-0658-4A2C-B2C8-79C647A48728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="67">
   <si>
     <t>Part Number</t>
   </si>
@@ -205,6 +205,27 @@
   </si>
   <si>
     <t>https://www.snapeda.com/parts/ESP32-DEVKIT-V1/Do+it/view-part/?ref=eda</t>
+  </si>
+  <si>
+    <t>TFT-ST7735</t>
+  </si>
+  <si>
+    <t>1.8 Inch 128x160</t>
+  </si>
+  <si>
+    <t>1.8 inches 128x160 RGB TFT LCD - ST7735 DRIVER</t>
+  </si>
+  <si>
+    <t>ST7735</t>
+  </si>
+  <si>
+    <t>SCH/TFT-ST7735.SchLib</t>
+  </si>
+  <si>
+    <t>PCB/TFT-ST7735.PcbLib</t>
+  </si>
+  <si>
+    <t>https://grabcad.com/library/1-8-inches-128x160-rgb-tft-lcd-st7735-driver-1</t>
   </si>
 </sst>
 </file>
@@ -611,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -907,6 +928,41 @@
         <v>59</v>
       </c>
     </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-30</v>
+      </c>
+      <c r="F9" s="2">
+        <v>80</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
@@ -917,6 +973,7 @@
     <hyperlink ref="K6" r:id="rId5" display="https://www.digikey.de/de/products/detail/omron-electronics-inc-emc-div/B3F-4055/31799?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=19971370784&amp;gbraid=0AAAAADrbLlgb8g5iB56Pq7GBfmlW8M2um&amp;gclid=CjwKCAiA2svIBhB-EiwARWDPjsxJrtH3aqZi4wzUZvXY0ugmwA-CuPqPru_7AumdmvXcQLZq2TM71hoCQyEQAvD_BwE" xr:uid="{E4FF004C-5A6C-4B6D-9D01-B58BD91062E9}"/>
     <hyperlink ref="K7" r:id="rId6" xr:uid="{78F5BECE-FB68-4FD0-9323-150479BC1E56}"/>
     <hyperlink ref="K8" r:id="rId7" xr:uid="{229173BB-844E-4007-BA9D-092EC23AECD2}"/>
+    <hyperlink ref="K9" r:id="rId8" xr:uid="{9E9D47BF-0437-4F4E-877C-47565310CD1B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BDD44A-0658-4A2C-B2C8-79C647A48728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A3F639-23F1-4136-ABAC-D72680F02114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1608" yWindow="17172" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="73">
   <si>
     <t>Part Number</t>
   </si>
@@ -226,6 +226,24 @@
   </si>
   <si>
     <t>https://grabcad.com/library/1-8-inches-128x160-rgb-tft-lcd-st7735-driver-1</t>
+  </si>
+  <si>
+    <t>ESP32-WROOM-32</t>
+  </si>
+  <si>
+    <t>Bluetooth, WiFi 802.11b/g/n, Bluetooth v4.2 +EDR, Class 1, 2 and 3 Transceiver Module U.FL Surface Mount</t>
+  </si>
+  <si>
+    <t>SCH/ESP32-WROOM-32.SchLib</t>
+  </si>
+  <si>
+    <t>MODULE_ESP32-WROOM-32</t>
+  </si>
+  <si>
+    <t>PCB/MODULE_ESP32-WROOM-32.PcbLib</t>
+  </si>
+  <si>
+    <t>https://documentation.espressif.com/esp32-wroom-32_datasheet_en.pdf</t>
   </si>
 </sst>
 </file>
@@ -632,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -963,6 +981,41 @@
         <v>66</v>
       </c>
     </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="2">
+        <v>-40</v>
+      </c>
+      <c r="F10" s="2">
+        <v>85</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
@@ -974,6 +1027,7 @@
     <hyperlink ref="K7" r:id="rId6" xr:uid="{78F5BECE-FB68-4FD0-9323-150479BC1E56}"/>
     <hyperlink ref="K8" r:id="rId7" xr:uid="{229173BB-844E-4007-BA9D-092EC23AECD2}"/>
     <hyperlink ref="K9" r:id="rId8" xr:uid="{9E9D47BF-0437-4F4E-877C-47565310CD1B}"/>
+    <hyperlink ref="K10" r:id="rId9" xr:uid="{1FE31FC4-2FC8-4A7C-8E01-2B38FA19CB9B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A3F639-23F1-4136-ABAC-D72680F02114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EB599E-25E3-453D-85BE-A47896BCBD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1608" yWindow="17172" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="80">
   <si>
     <t>Part Number</t>
   </si>
@@ -244,6 +244,27 @@
   </si>
   <si>
     <t>https://documentation.espressif.com/esp32-wroom-32_datasheet_en.pdf</t>
+  </si>
+  <si>
+    <t>EC11E15244G1</t>
+  </si>
+  <si>
+    <t>10mA 5V DC</t>
+  </si>
+  <si>
+    <t>EC11 Rotary Encoder with Switch</t>
+  </si>
+  <si>
+    <t>SCH/EC11E15244G1.SchLib</t>
+  </si>
+  <si>
+    <t>EC11E15244G1_AAL</t>
+  </si>
+  <si>
+    <t>PCB/EC11E15244G1.PcbLib</t>
+  </si>
+  <si>
+    <t>https://tech.alpsalpine.com/e/products/detail/EC11E15244G1/</t>
   </si>
 </sst>
 </file>
@@ -650,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -1016,6 +1037,41 @@
         <v>72</v>
       </c>
     </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-40</v>
+      </c>
+      <c r="F11" s="2">
+        <v>85</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
@@ -1028,6 +1084,7 @@
     <hyperlink ref="K8" r:id="rId7" xr:uid="{229173BB-844E-4007-BA9D-092EC23AECD2}"/>
     <hyperlink ref="K9" r:id="rId8" xr:uid="{9E9D47BF-0437-4F4E-877C-47565310CD1B}"/>
     <hyperlink ref="K10" r:id="rId9" xr:uid="{1FE31FC4-2FC8-4A7C-8E01-2B38FA19CB9B}"/>
+    <hyperlink ref="K11" r:id="rId10" xr:uid="{EF1685DD-C66B-4F3A-84B9-17CB22640930}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EB599E-25E3-453D-85BE-A47896BCBD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DF8577-26DB-4FBB-AB83-A253EEB98666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21705" yWindow="-12390" windowWidth="21810" windowHeight="18945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="99">
   <si>
     <t>Part Number</t>
   </si>
@@ -265,6 +265,63 @@
   </si>
   <si>
     <t>https://tech.alpsalpine.com/e/products/detail/EC11E15244G1/</t>
+  </si>
+  <si>
+    <t>0.8A, 15V</t>
+  </si>
+  <si>
+    <t>Linearer Spannungsregler, 800 mA, 15 V</t>
+  </si>
+  <si>
+    <t>AMS1117-3.3</t>
+  </si>
+  <si>
+    <t>SCH/AMS1117-3.3.SchLib</t>
+  </si>
+  <si>
+    <t>SOT229P700X180-4N</t>
+  </si>
+  <si>
+    <t>https://www.snapeda.com/parts/AMS1117-3.3/Advanced%20Monolithic%20Systems/datasheet/</t>
+  </si>
+  <si>
+    <t>PCB/SOT229P700X180-4N.PcbLib</t>
+  </si>
+  <si>
+    <t>6 Pos 3.5mm</t>
+  </si>
+  <si>
+    <t>6 Position Wire to Board Terminal Block Horizontal with Board 0.138" (3.50mm) Through Hole</t>
+  </si>
+  <si>
+    <t>SCH/1984659.SchLib</t>
+  </si>
+  <si>
+    <t>CONN_1984659_PXC</t>
+  </si>
+  <si>
+    <t>PCB/1984659.PcbLib</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/en/products/detail/phoenix-contact/1984659/950852</t>
+  </si>
+  <si>
+    <t>Capacitor 0805</t>
+  </si>
+  <si>
+    <t>ECHU1H101JX5</t>
+  </si>
+  <si>
+    <t>SCH/ECHU1H101JX5.SchLib</t>
+  </si>
+  <si>
+    <t>CAP_ECHU1H101JX5</t>
+  </si>
+  <si>
+    <t>PCB/CAP_ECHU1H101JX5.PcbLib</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -671,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -1072,6 +1129,111 @@
         <v>79</v>
       </c>
     </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="2">
+        <v>-40</v>
+      </c>
+      <c r="F12" s="2">
+        <v>125</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>1984659</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1984659</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="2">
+        <v>-40</v>
+      </c>
+      <c r="F13" s="2">
+        <v>125</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1984659</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="2">
+        <v>805</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="2">
+        <v>-40</v>
+      </c>
+      <c r="F14" s="2">
+        <v>125</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
@@ -1085,6 +1247,9 @@
     <hyperlink ref="K9" r:id="rId8" xr:uid="{9E9D47BF-0437-4F4E-877C-47565310CD1B}"/>
     <hyperlink ref="K10" r:id="rId9" xr:uid="{1FE31FC4-2FC8-4A7C-8E01-2B38FA19CB9B}"/>
     <hyperlink ref="K11" r:id="rId10" xr:uid="{EF1685DD-C66B-4F3A-84B9-17CB22640930}"/>
+    <hyperlink ref="K12" r:id="rId11" xr:uid="{EEB8497E-ED23-4CC8-BD1C-5A3542C6E0B3}"/>
+    <hyperlink ref="K13" r:id="rId12" xr:uid="{BBABDB8F-29DB-4F6B-8DC7-5674625D2A1D}"/>
+    <hyperlink ref="K14" r:id="rId13" display="https://www.digikey.de/en/products/detail/phoenix-contact/1984659/950852" xr:uid="{4EFC7E68-0237-41AA-A776-4A57A244EA86}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DF8577-26DB-4FBB-AB83-A253EEB98666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2C4CD7-3725-435F-9649-A9CE5D891F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21705" yWindow="-12390" windowWidth="21810" windowHeight="18945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2775" yWindow="3180" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="104">
   <si>
     <t>Part Number</t>
   </si>
@@ -309,19 +309,34 @@
     <t>Capacitor 0805</t>
   </si>
   <si>
-    <t>ECHU1H101JX5</t>
-  </si>
-  <si>
-    <t>SCH/ECHU1H101JX5.SchLib</t>
-  </si>
-  <si>
-    <t>CAP_ECHU1H101JX5</t>
-  </si>
-  <si>
-    <t>PCB/CAP_ECHU1H101JX5.PcbLib</t>
-  </si>
-  <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>CAP0805</t>
+  </si>
+  <si>
+    <t>PCB/Capacitor0805.PcbLib</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>SCH/C.SchLib</t>
+  </si>
+  <si>
+    <t>Resistor 1206</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>SCH/R.SchLib</t>
+  </si>
+  <si>
+    <t>RES1206</t>
+  </si>
+  <si>
+    <t>PCB/Resistor1206.PcbLib</t>
   </si>
 </sst>
 </file>
@@ -728,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -1213,25 +1228,60 @@
         <v>93</v>
       </c>
       <c r="E14" s="2">
-        <v>-40</v>
+        <v>-55</v>
       </c>
       <c r="F14" s="2">
         <v>125</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>98</v>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1206</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="2">
+        <v>-55</v>
+      </c>
+      <c r="F15" s="2">
+        <v>125</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1250,6 +1300,7 @@
     <hyperlink ref="K12" r:id="rId11" xr:uid="{EEB8497E-ED23-4CC8-BD1C-5A3542C6E0B3}"/>
     <hyperlink ref="K13" r:id="rId12" xr:uid="{BBABDB8F-29DB-4F6B-8DC7-5674625D2A1D}"/>
     <hyperlink ref="K14" r:id="rId13" display="https://www.digikey.de/en/products/detail/phoenix-contact/1984659/950852" xr:uid="{4EFC7E68-0237-41AA-A776-4A57A244EA86}"/>
+    <hyperlink ref="K15" r:id="rId14" display="https://www.digikey.de/en/products/detail/phoenix-contact/1984659/950852" xr:uid="{61CEF08A-6466-4F3A-A214-94AA9A82AD1E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2C4CD7-3725-435F-9649-A9CE5D891F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9701D0-C154-4D42-A0BA-5A7B3740FCC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2775" yWindow="3180" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="117">
   <si>
     <t>Part Number</t>
   </si>
@@ -337,6 +337,45 @@
   </si>
   <si>
     <t>PCB/Resistor1206.PcbLib</t>
+  </si>
+  <si>
+    <t>FS8205A</t>
+  </si>
+  <si>
+    <t>Dual N-Channel Enhancement Mode Power MOSFET</t>
+  </si>
+  <si>
+    <t>https://www.ic-fortune.com/upload/Download/FS8205A-DS-12_EN.pdf</t>
+  </si>
+  <si>
+    <t>SCH/FS8205A.SchLib</t>
+  </si>
+  <si>
+    <t>SOP65P640X120-8N</t>
+  </si>
+  <si>
+    <t>PCB/SOP65P640X120-8N.PcbLib</t>
+  </si>
+  <si>
+    <t>https://www.snapeda.com/parts/DW01A/Fortune%20Semiconductor/datasheet/</t>
+  </si>
+  <si>
+    <t>DW01A</t>
+  </si>
+  <si>
+    <t>SOT-23-6</t>
+  </si>
+  <si>
+    <t>One Cell Lithium-ion/Polymer Battery Protection IC</t>
+  </si>
+  <si>
+    <t>SCH/DW01A.SchLib</t>
+  </si>
+  <si>
+    <t>SOT95P280X145-6N</t>
+  </si>
+  <si>
+    <t>PCB/SOT95P280X145-6N.PcbLib</t>
   </si>
 </sst>
 </file>
@@ -743,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -1284,6 +1323,76 @@
         <v>94</v>
       </c>
     </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="2">
+        <v>-55</v>
+      </c>
+      <c r="F16" s="2">
+        <v>150</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="2">
+        <v>-40</v>
+      </c>
+      <c r="F17" s="2">
+        <v>85</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
@@ -1301,6 +1410,8 @@
     <hyperlink ref="K13" r:id="rId12" xr:uid="{BBABDB8F-29DB-4F6B-8DC7-5674625D2A1D}"/>
     <hyperlink ref="K14" r:id="rId13" display="https://www.digikey.de/en/products/detail/phoenix-contact/1984659/950852" xr:uid="{4EFC7E68-0237-41AA-A776-4A57A244EA86}"/>
     <hyperlink ref="K15" r:id="rId14" display="https://www.digikey.de/en/products/detail/phoenix-contact/1984659/950852" xr:uid="{61CEF08A-6466-4F3A-A214-94AA9A82AD1E}"/>
+    <hyperlink ref="K16" r:id="rId15" xr:uid="{B77A82F4-3998-4DD2-94A3-B3BFD0326F64}"/>
+    <hyperlink ref="K17" r:id="rId16" xr:uid="{7545D52A-58FE-49A2-8DE5-2E1490FE2768}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\OneDrive\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9701D0-C154-4D42-A0BA-5A7B3740FCC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7AC3D22-D9C9-4A9B-B827-98110FFF669D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="131">
   <si>
     <t>Part Number</t>
   </si>
@@ -376,6 +376,48 @@
   </si>
   <si>
     <t>PCB/SOT95P280X145-6N.PcbLib</t>
+  </si>
+  <si>
+    <t>MP1484EN-LF</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.925V 1 Output 3A</t>
+  </si>
+  <si>
+    <t>Buck Switching Regulator IC Positive Adjustable 0.925V 1 Output 3A 8-SOIC (0.154", 3.90mm Width)</t>
+  </si>
+  <si>
+    <t>SCH/MP1484EN-LF.SchLib</t>
+  </si>
+  <si>
+    <t>SOIC127P600X170-9N</t>
+  </si>
+  <si>
+    <t>PCB/SOIC127P600X170-9N.PcbLib</t>
+  </si>
+  <si>
+    <t>https://www.digikey.at/de/products/detail/monolithic-power-systems-inc/MP1484EN-LF-Z/5291682?srsltid=AfmBOorvZqZweepwF19jqwdCHLwo1ck00ZSGZEtpVPLNX4bN2FRk_ecr</t>
+  </si>
+  <si>
+    <t>TFT-ILI9488</t>
+  </si>
+  <si>
+    <t>3.5-inch TFT LCD (320 × 480)</t>
+  </si>
+  <si>
+    <t>3.5-inch TFT LCD (320 × 480) with ILI9488 driver + XPT2046 resistive touch</t>
+  </si>
+  <si>
+    <t>https://grabcad.com/library/3-5-color-spi-display-based-on-ili9488-chip-1</t>
+  </si>
+  <si>
+    <t>SCH/6130XX11121_61301411121.SchLib</t>
+  </si>
+  <si>
+    <t>PCB/61301411121.PcbLib</t>
+  </si>
+  <si>
+    <t>TFT_3.5_INCH</t>
   </si>
 </sst>
 </file>
@@ -502,9 +544,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Check Cell" xfId="1" builtinId="23"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Link" xfId="2" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Zelle überprüfen" xfId="1" builtinId="23"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -782,17 +824,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="19.85546875" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" customWidth="1"/>
-    <col min="4" max="4" width="84.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" customWidth="1"/>
+    <col min="4" max="4" width="90.7109375" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
     <col min="7" max="7" width="27.42578125" customWidth="1"/>
-    <col min="8" max="8" width="33.5703125" customWidth="1"/>
+    <col min="8" max="8" width="45" customWidth="1"/>
     <col min="9" max="9" width="30.140625" customWidth="1"/>
     <col min="10" max="10" width="43" customWidth="1"/>
     <col min="11" max="11" width="136.7109375" customWidth="1"/>
@@ -1391,6 +1433,76 @@
       </c>
       <c r="K17" s="5" t="s">
         <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="2">
+        <v>-20</v>
+      </c>
+      <c r="F18" s="2">
+        <v>85</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" s="2">
+        <v>-30</v>
+      </c>
+      <c r="F19" s="2">
+        <v>85</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="2">
+        <v>61301411121</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1412,6 +1524,8 @@
     <hyperlink ref="K15" r:id="rId14" display="https://www.digikey.de/en/products/detail/phoenix-contact/1984659/950852" xr:uid="{61CEF08A-6466-4F3A-A214-94AA9A82AD1E}"/>
     <hyperlink ref="K16" r:id="rId15" xr:uid="{B77A82F4-3998-4DD2-94A3-B3BFD0326F64}"/>
     <hyperlink ref="K17" r:id="rId16" xr:uid="{7545D52A-58FE-49A2-8DE5-2E1490FE2768}"/>
+    <hyperlink ref="K18" r:id="rId17" xr:uid="{1999A819-4DF6-4646-B0EA-9FF9A230FFB5}"/>
+    <hyperlink ref="K19" r:id="rId18" xr:uid="{94A68611-6BDD-45FD-B434-DBCCF4F72442}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\OneDrive\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7AC3D22-D9C9-4A9B-B827-98110FFF669D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F1234B-A6D0-4AD4-83A9-128BAC446898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21660" yWindow="6450" windowWidth="21765" windowHeight="18945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="137">
   <si>
     <t>Part Number</t>
   </si>
@@ -418,6 +418,24 @@
   </si>
   <si>
     <t>TFT_3.5_INCH</t>
+  </si>
+  <si>
+    <t>CH340C</t>
+  </si>
+  <si>
+    <t>USB to serial chip</t>
+  </si>
+  <si>
+    <t>SCH/CH340C.SchLib</t>
+  </si>
+  <si>
+    <t>SOIC127P600X180-16N</t>
+  </si>
+  <si>
+    <t>PCB/SOIC127P600X180-16N.PcbLib</t>
+  </si>
+  <si>
+    <t>https://www.snapeda.com/parts/CH340C/WCH/datasheet/</t>
   </si>
 </sst>
 </file>
@@ -544,9 +562,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Link" xfId="2" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
-    <cellStyle name="Zelle überprüfen" xfId="1" builtinId="23"/>
+    <cellStyle name="Check Cell" xfId="1" builtinId="23"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -824,8 +842,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="19.85546875" customWidth="1"/>
@@ -1503,6 +1521,41 @@
       </c>
       <c r="K19" s="5" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E20" s="2">
+        <v>-30</v>
+      </c>
+      <c r="F20" s="2">
+        <v>85</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1526,6 +1579,7 @@
     <hyperlink ref="K17" r:id="rId16" xr:uid="{7545D52A-58FE-49A2-8DE5-2E1490FE2768}"/>
     <hyperlink ref="K18" r:id="rId17" xr:uid="{1999A819-4DF6-4646-B0EA-9FF9A230FFB5}"/>
     <hyperlink ref="K19" r:id="rId18" xr:uid="{94A68611-6BDD-45FD-B434-DBCCF4F72442}"/>
+    <hyperlink ref="K20" r:id="rId19" xr:uid="{ACAB057F-4468-4B22-8C93-E8C22D24B65F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F1234B-A6D0-4AD4-83A9-128BAC446898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E05888A-862C-439D-8D87-8B4ADA3B1A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21660" yWindow="6450" windowWidth="21765" windowHeight="18945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="143">
   <si>
     <t>Part Number</t>
   </si>
@@ -436,6 +436,24 @@
   </si>
   <si>
     <t>https://www.snapeda.com/parts/CH340C/WCH/datasheet/</t>
+  </si>
+  <si>
+    <t>2POS 2.54MM</t>
+  </si>
+  <si>
+    <t>Connector Header Through Hole 2 position 0.100" (2.54mm)</t>
+  </si>
+  <si>
+    <t>SCH/22232021.SchLib</t>
+  </si>
+  <si>
+    <t>CONN_A-6373-02A_MOL</t>
+  </si>
+  <si>
+    <t>PCB/CONN_A-6373-02A_MOL.PcbLib</t>
+  </si>
+  <si>
+    <t>https://www.molex.com/en-us/products/part-detail/0022232021</t>
   </si>
 </sst>
 </file>
@@ -842,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -1556,6 +1574,41 @@
       </c>
       <c r="K20" s="5" t="s">
         <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>22232021</v>
+      </c>
+      <c r="B21" s="2">
+        <v>22232021</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21" s="2">
+        <v>-30</v>
+      </c>
+      <c r="F21" s="2">
+        <v>85</v>
+      </c>
+      <c r="G21" s="2">
+        <v>22232021</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1580,6 +1633,7 @@
     <hyperlink ref="K18" r:id="rId17" xr:uid="{1999A819-4DF6-4646-B0EA-9FF9A230FFB5}"/>
     <hyperlink ref="K19" r:id="rId18" xr:uid="{94A68611-6BDD-45FD-B434-DBCCF4F72442}"/>
     <hyperlink ref="K20" r:id="rId19" xr:uid="{ACAB057F-4468-4B22-8C93-E8C22D24B65F}"/>
+    <hyperlink ref="K21" r:id="rId20" xr:uid="{F4194E98-BFEF-4B12-A2C1-854A13CE3C9C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E05888A-862C-439D-8D87-8B4ADA3B1A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091F2723-497F-45EA-99ED-531C847873CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="159">
   <si>
     <t>Part Number</t>
   </si>
@@ -454,6 +454,54 @@
   </si>
   <si>
     <t>https://www.molex.com/en-us/products/part-detail/0022232021</t>
+  </si>
+  <si>
+    <t>USB4125-GF-A-0190</t>
+  </si>
+  <si>
+    <t>6 Pin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	CONN RCPT TYPE C 6P SMD RA</t>
+  </si>
+  <si>
+    <t>USB-C 2.0</t>
+  </si>
+  <si>
+    <t>SCH/USB4125-GF-A-0190_REVA2.SchLib</t>
+  </si>
+  <si>
+    <t>GCT_USB4125-GF-A-0190_REVA2</t>
+  </si>
+  <si>
+    <t>PCB/GCT_USB4125-GF-A-0190_REVA2.PcbLib</t>
+  </si>
+  <si>
+    <t>https://gct.co/files/specs/usb4125-spec.pdf</t>
+  </si>
+  <si>
+    <t>USB4105-GF-A-060</t>
+  </si>
+  <si>
+    <t>16 Pin</t>
+  </si>
+  <si>
+    <t>CONN RCP USB2.0 TYP C 16P SMD RA</t>
+  </si>
+  <si>
+    <t>USB Type C 16P</t>
+  </si>
+  <si>
+    <t>SCH/USB4105-GF-A-060.SchLib</t>
+  </si>
+  <si>
+    <t>GCT_USB4105-GF-A-060</t>
+  </si>
+  <si>
+    <t>PCB/GCT_USB4105-GF-A-060.PcbLib</t>
+  </si>
+  <si>
+    <t>https://gct.co/files/specs/usb4105-spec.pdf</t>
   </si>
 </sst>
 </file>
@@ -860,10 +908,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
     <col min="2" max="2" width="19.85546875" customWidth="1"/>
     <col min="3" max="3" width="28.140625" customWidth="1"/>
     <col min="4" max="4" width="90.7109375" customWidth="1"/>
@@ -1609,6 +1657,76 @@
       </c>
       <c r="K21" s="5" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E22" s="2">
+        <v>-30</v>
+      </c>
+      <c r="F22" s="2">
+        <v>85</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E23" s="2">
+        <v>-40</v>
+      </c>
+      <c r="F23" s="2">
+        <v>85</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -1634,6 +1752,8 @@
     <hyperlink ref="K19" r:id="rId18" xr:uid="{94A68611-6BDD-45FD-B434-DBCCF4F72442}"/>
     <hyperlink ref="K20" r:id="rId19" xr:uid="{ACAB057F-4468-4B22-8C93-E8C22D24B65F}"/>
     <hyperlink ref="K21" r:id="rId20" xr:uid="{F4194E98-BFEF-4B12-A2C1-854A13CE3C9C}"/>
+    <hyperlink ref="K22" r:id="rId21" xr:uid="{BE4EDFA5-F1AC-4169-B5FB-956CDB9ED25F}"/>
+    <hyperlink ref="K23" r:id="rId22" xr:uid="{6AEAE48E-4C59-41F2-BB06-858E00F21DE2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091F2723-497F-45EA-99ED-531C847873CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FDB582-FA21-4FE4-B122-592E25CBA535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21600" yWindow="-3405" windowWidth="21810" windowHeight="15930" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="165">
   <si>
     <t>Part Number</t>
   </si>
@@ -502,6 +502,24 @@
   </si>
   <si>
     <t>https://gct.co/files/specs/usb4105-spec.pdf</t>
+  </si>
+  <si>
+    <t>SRP1038AA-R36M</t>
+  </si>
+  <si>
+    <t>11 mm x 10 mm</t>
+  </si>
+  <si>
+    <t>SMD Inductor 11x10mm</t>
+  </si>
+  <si>
+    <t>SCH/SRP1038AA-R36M.SchLib</t>
+  </si>
+  <si>
+    <t>INDPM110100X400N</t>
+  </si>
+  <si>
+    <t>PCB/INDPM110100X400N.PcbLib</t>
   </si>
 </sst>
 </file>
@@ -908,7 +926,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -1726,6 +1744,41 @@
         <v>157</v>
       </c>
       <c r="K23" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24" s="2">
+        <v>-55</v>
+      </c>
+      <c r="F24" s="2">
+        <v>155</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K24" s="5" t="s">
         <v>158</v>
       </c>
     </row>
@@ -1754,6 +1807,7 @@
     <hyperlink ref="K21" r:id="rId20" xr:uid="{F4194E98-BFEF-4B12-A2C1-854A13CE3C9C}"/>
     <hyperlink ref="K22" r:id="rId21" xr:uid="{BE4EDFA5-F1AC-4169-B5FB-956CDB9ED25F}"/>
     <hyperlink ref="K23" r:id="rId22" xr:uid="{6AEAE48E-4C59-41F2-BB06-858E00F21DE2}"/>
+    <hyperlink ref="K24" r:id="rId23" xr:uid="{6FD8282A-76A1-4640-B675-63202C847A00}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/pcb/Library/MarbleLib.xlsx
+++ b/pcb/Library/MarbleLib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\pcb\Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FDB582-FA21-4FE4-B122-592E25CBA535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1953B766-4481-4664-8600-6432C7622567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-3405" windowWidth="21810" windowHeight="15930" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="179">
   <si>
     <t>Part Number</t>
   </si>
@@ -520,6 +520,48 @@
   </si>
   <si>
     <t>PCB/INDPM110100X400N.PcbLib</t>
+  </si>
+  <si>
+    <t>MMBT3904</t>
+  </si>
+  <si>
+    <t>NPN</t>
+  </si>
+  <si>
+    <t>TRANS NPN 40V 0.2A SOT23-3</t>
+  </si>
+  <si>
+    <t>SCH/MMBT3904.SchLib</t>
+  </si>
+  <si>
+    <t>TRANS_MMBT3904</t>
+  </si>
+  <si>
+    <t>PCB/TRANS_MMBT3904.PcbLib</t>
+  </si>
+  <si>
+    <t>https://diotec.com/request/datasheet/mmbt3904.pdf</t>
+  </si>
+  <si>
+    <t>SW_2-1825910-7</t>
+  </si>
+  <si>
+    <t>Button 6mm</t>
+  </si>
+  <si>
+    <t>Button 6mm x 6mm</t>
+  </si>
+  <si>
+    <t>2-1825910-7</t>
+  </si>
+  <si>
+    <t>PCB/SnapEDApcb.PcbLib</t>
+  </si>
+  <si>
+    <t>SCH/SnapEDAsch.SchLib</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/te-connectivity-alcoswitch-switches/2-1825910-7/1632528?srsltid=AfmBOorIgxPx8-RK9ZbRgtQifCi0fztvshC0t_fVXu46lzstz4pRWn6z</t>
   </si>
 </sst>
 </file>
@@ -926,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -1780,6 +1822,76 @@
       </c>
       <c r="K24" s="5" t="s">
         <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E25" s="2">
+        <v>-55</v>
+      </c>
+      <c r="F25" s="2">
+        <v>150</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E26" s="2">
+        <v>-55</v>
+      </c>
+      <c r="F26" s="2">
+        <v>150</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -1808,6 +1920,8 @@
     <hyperlink ref="K22" r:id="rId21" xr:uid="{BE4EDFA5-F1AC-4169-B5FB-956CDB9ED25F}"/>
     <hyperlink ref="K23" r:id="rId22" xr:uid="{6AEAE48E-4C59-41F2-BB06-858E00F21DE2}"/>
     <hyperlink ref="K24" r:id="rId23" xr:uid="{6FD8282A-76A1-4640-B675-63202C847A00}"/>
+    <hyperlink ref="K25" r:id="rId24" xr:uid="{2F56A580-236C-4EE5-8708-EFAAB7C6E460}"/>
+    <hyperlink ref="K26" r:id="rId25" xr:uid="{8F5D9F85-31B7-4924-AA8A-1D74C366D685}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
